--- a/每日预测/Aii竞彩推荐_2026-05-16.xlsx
+++ b/每日预测/Aii竞彩推荐_2026-05-16.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,9 +60,6 @@
       <color rgb="001A3C6E"/>
       <sz val="11"/>
     </font>
-    <font>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -97,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -163,17 +160,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,10 +186,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,9 +206,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -583,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -608,7 +596,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源：中国竞彩网(sporttery)+500.com · 00:24</t>
+          <t>数据来源：中国竞彩网(sporttery)+500.com · 20:47</t>
         </is>
       </c>
     </row>
@@ -688,7 +676,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -723,7 +711,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>SP2.60/2.78/2.60 让球-1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -735,7 +723,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -770,7 +758,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>SP2.75/3.15/2.23 让球+1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -782,7 +770,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -817,7 +805,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>SP2.70/3.15/2.27 让球+1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -829,7 +817,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -864,7 +852,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>SP3.08/3.32/1.99 让球+1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -876,7 +864,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -911,7 +899,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>SP2.00/3.50/2.91 让球-1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -923,7 +911,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -958,7 +946,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>SP1.39/3.80/6.85 让球-1</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -970,7 +958,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1005,7 +993,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP7.50/2.95/1.51 让球0</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1005,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -1052,7 +1040,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP1.71/3.30/4.75 让球0</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1052,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1099,7 +1087,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP3.85/3.25/1.78 让球0</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1099,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -1146,7 +1134,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP1.52/3.72/4.95 让球0</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1146,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1193,7 +1181,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>SP1.16/6.70/8.50 让球-2</t>
+          <t>SP1.16/6.70/8.50 让球0</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1193,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -1240,7 +1228,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>SP1.73/4.70/2.95 让球-2</t>
+          <t>SP10.50/1.15/8.50 让球0</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1240,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1287,7 +1275,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>SP1.78/4.00/3.15 让球-1</t>
+          <t>SP1.65/4.15/3.55 让球0</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1287,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -1334,7 +1322,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>SP2.35/3.59/2.35 让球-1</t>
+          <t>SP2.53/3.52/2.22 让球0</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1334,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1381,7 +1369,7 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>SP2.48/3.90/2.13 让球+1</t>
+          <t>SP2.74/3.55/2.07 让球0</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1381,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -1428,7 +1416,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>SP3.13/4.25/1.74 让球+1</t>
+          <t>SP3.32/4.30/1.68 让球0</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1428,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1475,7 +1463,7 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>SP3.15/4.00/1.78 让球+1</t>
+          <t>SP2.98/4.00/1.84 让球0</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1475,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -1522,7 +1510,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>SP4.10/4.56/1.50 让球+1</t>
+          <t>SP4.45/4.65/1.45 让球0</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1522,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1569,7 +1557,7 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>SP2.80/3.85/1.95 让球+1</t>
+          <t>SP2.36/3.80/2.26 让球0</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1569,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1616,7 +1604,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>SP4.55/3.67/1.57 让球+1</t>
+          <t>SP4.50/3.82/1.55 让球0</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1616,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1663,7 +1651,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP1.29/4.90/6.70 让球0</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1663,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -1710,7 +1698,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.15/2.95/3.08 让球0</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1710,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1757,7 +1745,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP1.48/3.70/5.45 让球0</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1757,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -1804,7 +1792,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>SP1.53/3.80/4.70 让球-1</t>
+          <t>SP1.53/3.80/4.70 让球0</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1804,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1851,7 +1839,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>SP1.27/4.55/8.20 让球-1</t>
+          <t>SP1.30/4.50/7.25 让球0</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1851,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -1898,7 +1886,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP1.15/6.10/10.50 让球0</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1898,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1945,7 +1933,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>SP2.45/3.90/2.15 让球-2</t>
+          <t>SP0.00/0.00/0.00 让球0</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1945,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1992,7 +1980,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>SP9.50/5.70/1.18 让球+2</t>
+          <t>SP9.50/5.70/1.18 让球0</t>
         </is>
       </c>
     </row>
@@ -2004,7 +1992,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2039,7 +2027,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.55/3.46/2.23 让球0</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2039,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2086,14 +2074,14 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>SP0.00/0.00/0.00 让球0</t>
+          <t>SP2.16/3.20/2.83 让球0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>📊 SP数据 · 欧赔(spf)主分析·竞彩SP(nspf)对比 · 00:24</t>
+          <t>📊 赔率数据 · 欧赔(TheOddsAPI)·竞彩SP(sporttery)·让球SP(500.com) · 20:47</t>
         </is>
       </c>
     </row>
@@ -2165,33 +2153,39 @@
           <t>水户蜀葵vs东京绿茵</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E45" s="6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>2.6</v>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>1.36</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2211,33 +2205,39 @@
           <t>浦和红钻vs东京FC</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>2.23</v>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>5.00</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2257,33 +2257,39 @@
           <t>大田市民vs首尔FC</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E47" s="6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>2.27</v>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>5.20</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2303,33 +2309,39 @@
           <t>横滨水手vs柏太阳神</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1.99</v>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>4.20</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2349,33 +2361,39 @@
           <t>纽喷气机vs悉尼FC</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>2.91</v>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>1.61</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2395,33 +2413,39 @@
           <t>仁川联vs光州FC</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>6.85</v>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>2.50</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -2441,34 +2465,34 @@
           <t>赫尔辛基vs坦山猫</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6" t="n">
-        <v>0</v>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H51" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="52">
@@ -2487,34 +2511,34 @@
           <t>布兰vs奥斯KFUM</t>
         </is>
       </c>
-      <c r="D52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>0</v>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H52" s="7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="53">
@@ -2533,34 +2557,34 @@
           <t>哈尔姆斯vs埃夫斯堡</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>0</v>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H53" s="6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="54">
@@ -2579,34 +2603,34 @@
           <t>盖斯vs代格福什</t>
         </is>
       </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>0</v>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J54" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H54" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="55">
@@ -2625,34 +2649,34 @@
           <t>勒沃库森vs汉堡</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
         <v>1.16</v>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="I55" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="J55" s="6" t="n">
         <v>8.5</v>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
       </c>
     </row>
     <row r="56">
@@ -2671,34 +2695,34 @@
           <t>拜仁vs科隆</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>2.95</v>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="57">
@@ -2717,34 +2741,34 @@
           <t>海登海姆vs美因茨</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>3.15</v>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>3.96</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>3.55</v>
       </c>
     </row>
     <row r="58">
@@ -2763,34 +2787,34 @@
           <t>圣保利vs沃夫斯堡</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>2.35</v>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>5.15</t>
-        </is>
-      </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>2.22</v>
       </c>
     </row>
     <row r="59">
@@ -2809,34 +2833,34 @@
           <t>柏林联合vs奥格斯堡</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>2.13</v>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="60">
@@ -2855,34 +2879,34 @@
           <t>法兰克福vs斯图加特</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>1.74</v>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="61">
@@ -2901,34 +2925,34 @@
           <t>不来梅vs多特蒙德</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E61" s="6" t="n">
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I61" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F61" s="6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
+      <c r="J61" s="6" t="n">
+        <v>1.84</v>
       </c>
     </row>
     <row r="62">
@@ -2947,34 +2971,34 @@
           <t>门兴vs霍芬海姆</t>
         </is>
       </c>
-      <c r="D62" s="7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>1.5</v>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="63">
@@ -2993,34 +3017,34 @@
           <t>弗赖堡vs莱红牛</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E63" s="6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>1.95</v>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>2.26</v>
       </c>
     </row>
     <row r="64">
@@ -3039,34 +3063,34 @@
           <t>切尔西vs曼城</t>
         </is>
       </c>
-      <c r="D64" s="7" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>1.57</v>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>+1</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="65">
@@ -3085,34 +3109,34 @@
           <t>博德闪耀vs特罗姆瑟</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>0</v>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H65" s="6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>6.7</v>
       </c>
     </row>
     <row r="66">
@@ -3131,34 +3155,34 @@
           <t>赫尔火花vs雅罗</t>
         </is>
       </c>
-      <c r="D66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>0</v>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H66" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="67">
@@ -3177,34 +3201,34 @@
           <t>AC奥卢vsTPS图尔</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>0</v>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H67" s="6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>5.45</v>
       </c>
     </row>
     <row r="68">
@@ -3223,34 +3247,34 @@
           <t>布拉加vs阿马多拉</t>
         </is>
       </c>
-      <c r="D68" s="7" t="n">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n">
         <v>1.53</v>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="I68" s="7" t="n">
         <v>3.8</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="J68" s="7" t="n">
         <v>4.7</v>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
       </c>
     </row>
     <row r="69">
@@ -3269,34 +3293,34 @@
           <t>利雅胜利vs大阪钢巴</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>8.199999999999999</v>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>3.63</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>7.25</v>
       </c>
     </row>
     <row r="70">
@@ -3315,34 +3339,34 @@
           <t>吉达国民vs拉斯永恒</t>
         </is>
       </c>
-      <c r="D70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>0</v>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H70" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="71">
@@ -3361,33 +3385,39 @@
           <t>里斯本vs吉维森特</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>2.15</v>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>2.15</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>暂无</t>
         </is>
       </c>
     </row>
@@ -3407,34 +3437,34 @@
           <t>埃斯托里vs本菲卡</t>
         </is>
       </c>
-      <c r="D72" s="7" t="n">
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>10.12</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>6.49</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="n">
         <v>9.5</v>
       </c>
-      <c r="E72" s="7" t="n">
+      <c r="I72" s="7" t="n">
         <v>5.7</v>
       </c>
-      <c r="F72" s="7" t="n">
+      <c r="J72" s="7" t="n">
         <v>1.18</v>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
       </c>
     </row>
     <row r="73">
@@ -3453,34 +3483,34 @@
           <t>纽约红牛vs纽约城</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>0</v>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H73" s="6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="74">
@@ -3499,34 +3529,34 @@
           <t>新英格兰vs明尼苏达</t>
         </is>
       </c>
-      <c r="D74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>0</v>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="H74" s="7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="78">
@@ -3589,314 +3619,314 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>周六001</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>水户蜀葵vs东京绿茵</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=32%P客=32%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-1=输盘/让胜</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>周六002</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>浦和红钻vs东京FC</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=31%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球+1=走水/让平</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>周六003</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>大田市民vs首尔FC</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=36%P平=31%P客=33%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球+1=走水/让平</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>周六004</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>横滨水手vs柏太阳神</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>负负</t>
-        </is>
-      </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=35%P平=30%P客=35%|泊松比分0-1|半全场负负|大小球小2.5(41%)|让球+1=输盘/让胜</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>周六005</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>纽喷气机vs悉尼FC</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>2/10</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=43%P平=28%P客=29%|泊松比分1-0|半全场胜胜|大小球小2.5(44%)|让球-1=输盘/让胜</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>周六006</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>仁川联vs光州FC</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>3/10</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>胜胜</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>平胜</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>不投</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>贝叶斯P主=49%P平=27%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球-1=输盘/让胜</t>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3953,7 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3946,165 +3976,165 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>无有效SP数据，跳过</t>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>贝叶斯P主=33%P平=28%P客=40%|Poisson/Poisson比分0-1|半全场—|大小球小2.5(38%)|让球0=无让球/—|赔变主↓2% 平↑3% 客↑2%|放弃</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>周六008</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>布兰vs奥斯KFUM</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P主=46%P平=26%P客=28%|Poisson/Poisson比分2-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>周六009</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>哈尔姆斯vs埃夫斯堡</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H88" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>负负</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=38%|泊松比分0-1|半全场平负|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>周六010</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>盖斯vs代格福什</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=48%|泊松比分2-0|半全场胜胜|大小球小2.5(44%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4154,9 +4184,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=51%P平=24%P客=26%|泊松比分3-2|半全场胜胜|大小球大2.5(72%)|让球-2=输盘/让胜⚠️让-2深盘·主胜可能不穿盘</t>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=55%|泊松比分3-2|半全场胜胜|大小球大2.5(74%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4173,32 +4203,32 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -4206,9 +4236,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=50%P平=24%P客=26%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-2=输盘/让胜⚠️让-2深盘·主胜可能不穿盘</t>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
@@ -4258,9 +4288,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=46%P平=26%P客=29%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球-1=输盘/让胜</t>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=48%|泊松比分2-1|半全场胜胜|大小球大2.5(71%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4282,17 +4312,17 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -4310,9 +4340,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=40%P平=28%P客=33%|泊松比分2-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=40%|泊松比分3-2|半全场胜胜|大小球大2.5(73%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4364,7 @@
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>3/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
@@ -4362,9 +4392,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=38%P平=27%P客=35%|泊松比分2-1|半全场胜胜|大小球大2.5(67%)|让球+1=走水/让平</t>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=39%|泊松比分2-1|半全场胜胜|大小球大2.5(69%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4416,7 @@
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -4396,27 +4426,27 @@
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
           <t>负负</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>平负</t>
-        </is>
-      </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=35%P平=27%P客=38%|泊松比分0-1|半全场负负|大小球小2.5(44%)|让球+1=输盘/让胜</t>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=40%|泊松比分0-1|半全场平负|大小球小2.5(47%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4468,7 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -4466,9 +4496,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=32%P平=25%P客=43%|泊松比分1-3|半全场负负|大小球大2.5(73%)|让球+1=输盘/让胜</t>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=43%|泊松比分1-3|半全场负负|大小球大2.5(75%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4520,7 @@
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -4500,7 +4530,7 @@
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -4518,9 +4548,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=35%P平=25%P客=40%|泊松比分2-3|半全场负负|大小球大2.5(73%)|让球+1=输盘/让胜</t>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=44%|泊松比分2-3|半全场负负|大小球大2.5(75%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4542,19 +4572,19 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
           <t>负负</t>
@@ -4570,9 +4600,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=34%P平=26%P客=40%|泊松比分1-3|半全场负负|大小球大2.5(70%)|让球+1=输盘/让胜</t>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=39%|泊松比分1-2|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4622,165 +4652,165 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=29%P平=27%P客=44%|泊松比分1-3|半全场负负|大小球大2.5(69%)|让球+1=输盘/让胜</t>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=45%|泊松比分1-3|半全场负负|大小球大2.5(69%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>周六021</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>博德闪耀vs特罗姆瑟</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=50%|泊松比分2-0|半全场胜胜|大小球小2.5(45%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>周六022</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>赫尔火花vs雅罗</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=43%|泊松比分1-0|半全场平胜|大小球小2.5(41%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>周六023</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>AC奥卢vsTPS图尔</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=48%|泊松比分2-0|半全场胜胜|大小球小2.5(42%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4830,9 +4860,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=52%P平=26%P客=22%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球-1=输盘/让胜</t>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=54%|泊松比分3-1|半全场胜胜|大小球大2.5(70%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4882,61 +4912,61 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J104" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=50%P平=26%P客=24%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球-1=输盘/让胜</t>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=50%|泊松比分2-0|半全场胜胜|大小球小2.5(46%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>周六026</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>吉达国民vs拉斯永恒</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I105" s="7" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J105" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=52%|泊松比分2-0|半全场胜胜|大小球小2.5(48%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
@@ -4953,32 +4983,32 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>2/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>胜胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>平胜</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
@@ -4986,9 +5016,9 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J106" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=38%P平=28%P客=34%|泊松比分1-0|半全场胜胜|大小球小2.5(42%)|让球-2=输盘/让胜⚠️让-2深盘·主胜可能不穿盘</t>
+      <c r="J106" s="10" t="inlineStr">
+        <is>
+          <t>无有效SP数据，跳过</t>
         </is>
       </c>
     </row>
@@ -5038,120 +5068,120 @@
           <t>2元</t>
         </is>
       </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>贝叶斯P主=25%P平=24%P客=52%|泊松比分1-4|半全场负负|大小球大2.5(72%)|让球+2=输盘/让胜⚠️让+2深盘·客胜可能不穿盘</t>
+      <c r="J107" s="10" t="inlineStr">
+        <is>
+          <t>贝叶斯P=52%|泊松比分1-4|半全场负负|大小球大2.5(72%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>周六029</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>纽约红牛vs纽约城</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I108" s="7" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>平负</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J108" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=39%|泊松比分1-0|半全场平胜|大小球小2.5(43%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>周六030</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>新英格兰vs明尼苏达</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
-        <is>
-          <t>不投</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>1/10</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I109" s="7" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>胜胜</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>平胜</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
       <c r="J109" s="10" t="inlineStr">
         <is>
-          <t>无有效SP数据，跳过</t>
+          <t>贝叶斯P=42%|泊松比分1-0|半全场胜胜|大小球小2.5(43%)|让球0=无让球/—</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>🏆 14场胜负彩+任选9（第26075期 停售2026-05-13 22:00）</t>
+          <t>🏆 14场胜负彩+任选9（第26076期 停售2026-05-16 22:45）</t>
         </is>
       </c>
     </row>
@@ -5208,54 +5238,54 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
-        <is>
-          <t>英超</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>英足总杯</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>切尔西</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>曼彻斯特城</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>水晶宫</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F115" s="11" t="inlineStr">
-        <is>
-          <t>4.8/10</t>
-        </is>
-      </c>
-      <c r="G115" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr">
-        <is>
-          <t>★胆</t>
-        </is>
-      </c>
-      <c r="I115" s="11" t="inlineStr">
-        <is>
-          <t>P主=49%</t>
-        </is>
-      </c>
-      <c r="J115" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>客胜/平局</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>1/10</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>P主=34%P平=24%P客=42%</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5267,17 +5297,17 @@
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>意大利杯</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>拉齐奥</t>
+          <t>拜仁慕尼黑</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>国际米兰</t>
+          <t>科隆</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -5292,7 +5322,7 @@
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -5302,64 +5332,64 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>P主=32%P平=27%P客=41%</t>
+          <t>P主=0%P平=0%P客=0%</t>
         </is>
       </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>西班牙人</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>毕尔巴鄂竞技</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F117" s="11" t="inlineStr">
-        <is>
-          <t>4.0/10</t>
-        </is>
-      </c>
-      <c r="G117" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H117" s="11" t="inlineStr">
-        <is>
-          <t>★胆</t>
-        </is>
-      </c>
-      <c r="I117" s="11" t="inlineStr">
-        <is>
-          <t>P主=46%</t>
-        </is>
-      </c>
-      <c r="J117" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>弗赖堡</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>莱比锡红牛</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>4.2/10</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>P客=43%</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5371,32 +5401,32 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>比利亚雷亚尔</t>
+          <t>法兰克福</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>塞维利亚</t>
+          <t>斯图加特</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>3.6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -5406,116 +5436,116 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>P主=41%P平=28%P客=31%</t>
+          <t>P主=35%P平=25%P客=40%</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>阿拉维斯</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>巴塞罗那</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>客胜/平局</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>3.7/10</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>P主=31%P平=27%P客=42%</t>
-        </is>
-      </c>
-      <c r="J119" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>海登海姆</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>美因茨</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I119" s="11" t="inlineStr">
+        <is>
+          <t>P主=48% 优势19%</t>
+        </is>
+      </c>
+      <c r="J119" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="inlineStr">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>赫塔费</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>马洛卡</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>3.3/10</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H120" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>P主=38%P平=29%P客=33%</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>勒沃库森</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>汉堡</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>4/10</t>
+        </is>
+      </c>
+      <c r="G120" s="11" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="H120" s="11" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="inlineStr">
+        <is>
+          <t>P主=55% 优势30%</t>
+        </is>
+      </c>
+      <c r="J120" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5527,32 +5557,32 @@
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>巴伦西亚</t>
+          <t>门兴格拉德巴赫</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>巴列卡诺</t>
+          <t>霍芬海姆</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>3.6/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -5562,64 +5592,64 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>P主=41%P平=28%P客=31%</t>
+          <t>P主=34%P平=22%P客=44%</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="A122" s="11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>西甲</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>赫罗纳</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>皇家社会</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>主胜/平局</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>3.6/10</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>P主=41%P平=28%P客=32%</t>
-        </is>
-      </c>
-      <c r="J122" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>德甲</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>圣保利</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>沃尔夫斯堡</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>4.4/10</t>
+        </is>
+      </c>
+      <c r="G122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H122" s="11" t="inlineStr">
+        <is>
+          <t>★胆</t>
+        </is>
+      </c>
+      <c r="I122" s="11" t="inlineStr">
+        <is>
+          <t>P主=45%</t>
+        </is>
+      </c>
+      <c r="J122" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5631,17 +5661,17 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>皇家马德里</t>
+          <t>柏林联合</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>皇家奥维耶多</t>
+          <t>奥格斯堡</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -5651,12 +5681,12 @@
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>3.5/10</t>
+          <t>1/10</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -5666,12 +5696,12 @@
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>P主=40%P平=30%P客=30%</t>
+          <t>P主=39%P平=25%P客=36%</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5683,32 +5713,32 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>法甲</t>
+          <t>德甲</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>布雷斯特</t>
+          <t>云达不来梅</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>斯特拉斯堡</t>
+          <t>多特蒙德</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>3.4/10</t>
+          <t>2/10</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -5718,12 +5748,12 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>P主=37%P平=28%P客=34%</t>
+          <t>P主=35%P平=21%P客=43%</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
     </row>
@@ -5735,32 +5765,32 @@
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>法甲</t>
+          <t>葡超</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>朗斯</t>
+          <t>布拉加</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>巴黎圣日尔曼</t>
+          <t>阿马多拉</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>3.5/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -5770,12 +5800,12 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>P主=38%P平=29%P客=33%</t>
+          <t>P主=54% 优势28%</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -5787,32 +5817,32 @@
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>葡超</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>辛辛那提FC</t>
+          <t>埃斯托里尔</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>迈阿密国际</t>
+          <t>本菲卡</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>4/10</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -5822,12 +5852,12 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>P主=39%P平=30%P客=30%</t>
+          <t>P客=52% 优势22%</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -5839,22 +5869,22 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>葡超</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>圣路易斯城</t>
+          <t>里斯本竞技</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>洛杉矶FC</t>
+          <t>吉维森特</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>主胜/平局</t>
+          <t>客胜/平局</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
@@ -5864,7 +5894,7 @@
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -5874,12 +5904,12 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>P主=39%P平=30%P客=30%</t>
+          <t>P主=0%P平=0%P客=0%</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -5891,17 +5921,17 @@
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>挪超</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>西雅图海湾人</t>
+          <t>莫尔德</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>圣何塞地震</t>
+          <t>克里斯蒂安松</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -5911,7 +5941,7 @@
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>1/10</t>
+          <t>2.5/10</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5926,82 +5956,82 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>P主=39%P平=30%P客=30%</t>
+          <t>P主=41%P平=28%P客=31%</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>📋 任选9方案（2胆+7双=128注=256元）</t>
+          <t>📋 任选9方案（3胆+6双=64注=128元）</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1. 主胜           (信心4.8/10)</t>
+          <t xml:space="preserve">   8. 主胜           (信心4.4/10)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. 主胜           (信心4.0/10)</t>
+          <t xml:space="preserve">   3. 客胜           (信心4.2/10)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5. 客胜/平局        (信心3.7/10)</t>
+          <t xml:space="preserve">   5. 主胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4. 主胜/平局        (信心3.6/10)</t>
+          <t xml:space="preserve">   6. 主胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7. 主胜/平局        (信心3.6/10)</t>
+          <t xml:space="preserve">  11. 主胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8. 主胜/平局        (信心3.6/10)</t>
+          <t xml:space="preserve">  12. 客胜           (信心4/10)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   9. 主胜/平局        (信心3.5/10)</t>
+          <t xml:space="preserve">  14. 主胜/平局        (信心2.5/10)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. 主胜/平局        (信心3.5/10)</t>
+          <t xml:space="preserve">   4. 客胜/平局        (信心2/10)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. 主胜/平局        (信心3.4/10)</t>
+          <t xml:space="preserve">   7. 客胜/平局        (信心2/10)</t>
         </is>
       </c>
     </row>
@@ -6048,15 +6078,15 @@
           <t>2串1</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012</t>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>周六011+周六013</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)</t>
+·海登海姆:主胜(1.65)</t>
         </is>
       </c>
       <c r="D145" s="6" t="n">
@@ -6069,12 +6099,12 @@
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
         <is>
-          <t>1.16×1.73=2.01</t>
+          <t>1.16×1.65=1.91</t>
         </is>
       </c>
     </row>
@@ -6084,16 +6114,16 @@
           <t>3串1</t>
         </is>
       </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013</t>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>周六011+周六013+周六024</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)</t>
+·海登海姆:主胜(1.65)
+·布拉加:主胜(1.53)</t>
         </is>
       </c>
       <c r="D146" s="6" t="n">
@@ -6106,12 +6136,12 @@
       </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>1.16×1.73×1.78=3.57</t>
+          <t>1.16×1.65×1.53=2.93</t>
         </is>
       </c>
     </row>
@@ -6121,17 +6151,17 @@
           <t>4串1</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016</t>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>周六011+周六013+周六024+周六028</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)</t>
+·海登海姆:主胜(1.65)
+·布拉加:主胜(1.53)
+·埃斯托里:客胜(1.18)</t>
         </is>
       </c>
       <c r="D147" s="6" t="n">
@@ -6144,149 +6174,114 @@
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>1.16×1.73×1.78×1.74=6.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)
-·不来梅:客胜(1.78)</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>1.16×1.73×1.78×1.74×1.78=11.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017+周六018</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)
-·不来梅:客胜(1.78)
-·门兴:客胜(1.50)</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>16.60</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="inlineStr">
-        <is>
-          <t>1.16×1.73×1.78×1.74×1.78×1.50=16.60</t>
+          <t>1.16×1.65×1.53×1.18=3.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ 核心信号</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>场次</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>解读</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>应对</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ 核心信号</t>
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>🟢 高信心(4/10+)</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>周六011/周六013/周六024/周六028</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>4场贝叶斯概率最高</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>作胆材/串关核心</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>场次</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>解读</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>应对</t>
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>🟢 让球SP真实数据</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>全部场次</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>从500.com让球页提取，非估算</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>可用作让球分析</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>🟢 高信心(4/10+)</t>
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>🟡 平局候选</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>周六011/周六012/周六013/周六016/周六017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>9场贝叶斯概率最高</t>
+          <t>0场平局概率30%+</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>作胆材/串关核心</t>
+          <t>双选或慎入</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>🟢 让球SP真实数据</t>
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>🟡 让球数真实</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
@@ -6296,54 +6291,10 @@
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>从500.com让球页提取，非估算</t>
+          <t>从500.com data-rangqiu提取</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>可用作让球分析</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>🟡 平局候选</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>周六001/周六002/周六003</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>3场平局概率30%+</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>双选或慎入</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="8" t="inlineStr">
-        <is>
-          <t>🟡 让球数真实</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>全部场次</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>从500.com data-rangqiu提取</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
         <is>
           <t>让球分析可靠</t>
         </is>
@@ -6362,7 +6313,6 @@
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A153:J153"/>
     <mergeCell ref="A137:J137"/>
     <mergeCell ref="A133:J133"/>
     <mergeCell ref="A3:J3"/>
@@ -6370,6 +6320,7 @@
     <mergeCell ref="A139:J139"/>
     <mergeCell ref="A113:J113"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A151:J151"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6398,578 +6349,608 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六001 水户蜀葵 vs 东京绿茵 [日职] 13:00</t>
+          <t>⚽ 周六001 水户蜀葵 vs 东京绿茵 [日职] —</t>
         </is>
       </c>
     </row>
     <row r="4" ht="130" customHeight="1">
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：13:00
+          <t xml:space="preserve">时间：—
 联赛：日职
-欧赔(spf)：2.6 / 2.78 / 2.6
-差值分析：P主=36% P平=32% P客=32%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六002 浦和红钻 vs 东京FC [日职] 15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：15:00
-联赛：日职
-欧赔(spf)：2.75 / 3.15 / 2.23
-差值分析：P主=36% P平=31% P客=33%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让+1 走水=让平 </t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六003 大田市民 vs 首尔FC [韩职] 15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="130" customHeight="1">
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：15:30
-联赛：韩职
-欧赔(spf)：2.7 / 3.15 / 2.27
-差值分析：P主=36% P平=31% P客=33%
-推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
-让球:让+1 走水=让平 </t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六004 横滨水手 vs 柏太阳神 [日职] 16:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="130" customHeight="1">
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：16:00
-联赛：日职
-欧赔(spf)：3.08 / 3.32 / 1.99
-差值分析：P主=35% P平=30% P客=35%
-推荐：客胜 信心2/10 比分0-1(泊松) 半全场负负 大小球小2.5(41%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六005 纽喷气机 vs 悉尼FC [澳超] 17:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="130" customHeight="1">
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：17:40
-联赛：澳超
-欧赔(spf)：2.0 / 3.5 / 2.91
-差值分析：P主=43% P平=28% P客=29%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六006 仁川联 vs 光州FC [韩职] 18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="130" customHeight="1">
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：18:00
-联赛：韩职
-欧赔(spf)：1.39 / 3.8 / 6.85
-差值分析：P主=49% P平=27% P客=24%
-推荐：主胜 信心3/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六007 赫尔辛基 vs 坦山猫 [芬超] 19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="130" customHeight="1">
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：19:00
-联赛：芬超
-欧赔(spf)：0.0 / 0.0 / 0.0
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六008 布兰 vs 奥斯KFUM [挪超] 20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="130" customHeight="1">
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：20:00
-联赛：挪超
-欧赔(spf)：0.0 / 0.0 / 0.0
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六002 浦和红钻 vs 东京FC [日职] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：日职
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六009 哈尔姆斯 vs 埃夫斯堡 [瑞超] 21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="130" customHeight="1">
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:00
-联赛：瑞超
-欧赔(spf)：0.0 / 0.0 / 0.0
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六003 大田市民 vs 首尔FC [韩职] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="130" customHeight="1">
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：韩职
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六010 盖斯 vs 代格福什 [瑞超] 21:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="130" customHeight="1">
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:00
-联赛：瑞超
-欧赔(spf)：0.0 / 0.0 / 0.0
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六004 横滨水手 vs 柏太阳神 [日职] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="130" customHeight="1">
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：日职
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六011 勒沃库森 vs 汉堡 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="130" customHeight="1">
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>时间：21:30
-联赛：德甲
-欧赔(spf)：1.16 / 6.7 / 8.5
-差值分析：P主=51% P平=24% P客=26%
-推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(72%) 备选半全场:负胜
-让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六012 拜仁 vs 科隆 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="130" customHeight="1">
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>时间：21:30
-联赛：德甲
-欧赔(spf)：1.73 / 4.7 / 2.95
-差值分析：P主=50% P平=24% P客=26%
-推荐：主胜 信心4/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
-让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六013 海登海姆 vs 美因茨 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="130" customHeight="1">
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：1.78 / 4.0 / 3.15
-差值分析：P主=46% P平=26% P客=29%
-推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六014 圣保利 vs 沃夫斯堡 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="130" customHeight="1">
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：2.35 / 3.59 / 2.35
-差值分析：P主=40% P平=28% P客=33%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:负胜
-让球:让-1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六015 柏林联合 vs 奥格斯堡 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="130" customHeight="1">
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：2.48 / 3.9 / 2.13
-差值分析：P主=38% P平=27% P客=35%
-推荐：主胜 信心3/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(67%) 备选半全场:平胜
-让球:让+1 走水=让平 </t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六016 法兰克福 vs 斯图加特 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="130" customHeight="1">
-      <c r="B124" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：3.13 / 4.25 / 1.74
-差值分析：P主=35% P平=27% P客=38%
-推荐：客胜 信心4/10 比分0-1(泊松) 半全场负负 大小球小2.5(44%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六017 不来梅 vs 多特蒙德 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="130" customHeight="1">
-      <c r="B132" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：3.15 / 4.0 / 1.78
-差值分析：P主=32% P平=25% P客=43%
-推荐：客胜 信心4/10 比分1-3(泊松) 半全场负负 大小球大2.5(73%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六018 门兴 vs 霍芬海姆 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="130" customHeight="1">
-      <c r="B140" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：4.1 / 4.56 / 1.5
-差值分析：P主=35% P平=25% P客=40%
-推荐：客胜 信心4/10 比分2-3(泊松) 半全场负负 大小球大2.5(73%) 备选半全场:胜负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六019 弗赖堡 vs 莱红牛 [德甲] 21:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="130" customHeight="1">
-      <c r="B148" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：21:30
-联赛：德甲
-欧赔(spf)：2.8 / 3.85 / 1.95
-差值分析：P主=34% P平=26% P客=40%
-推荐：客胜 信心4/10 比分1-3(泊松) 半全场负负 大小球大2.5(70%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六020 切尔西 vs 曼城 [英足总杯] 22:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="130" customHeight="1">
-      <c r="B156" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：22:00
-联赛：英足总杯
-欧赔(spf)：4.55 / 3.67 / 1.57
-差值分析：P主=29% P平=27% P客=44%
-推荐：客胜 信心1/10 比分1-3(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
-让球:让+1 输盘=让胜 </t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六021 博德闪耀 vs 特罗姆瑟 [挪超] 00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="130" customHeight="1">
-      <c r="B164" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：00:00
-联赛：挪超
-欧赔(spf)：0.0 / 0.0 / 0.0
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六005 纽喷气机 vs 悉尼FC [澳超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="130" customHeight="1">
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：澳超
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="14" t="inlineStr">
-        <is>
-          <t>⚽ 周六022 赫尔火花 vs 雅罗 [芬超] 00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="130" customHeight="1">
-      <c r="B172" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">时间：00:00
-联赛：芬超
-欧赔(spf)：0.0 / 0.0 / 0.0
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六006 仁川联 vs 光州FC [韩职] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="130" customHeight="1">
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：韩职
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
 差值分析：P主=0% P平=0% P客=0%
 推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
 让球:让0 —=— </t>
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六007 赫尔辛基 vs 坦山猫 [芬超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="130" customHeight="1">
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：芬超
+欧赔：0.00/0.00/0.00
+竞彩SP：7.5 / 2.95 / 1.51
+差值分析：P主=33% P平=28% P客=40%
+推荐：不投 信心1/10 比分0-1(泊松) 半全场— 大小球小2.5(38%) 备选半全场:—
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六008 布兰 vs 奥斯KFUM [挪超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="130" customHeight="1">
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：挪超
+欧赔：0.00/0.00/0.00
+竞彩SP：1.71 / 3.3 / 4.75
+差值分析：P主=46% P平=26% P客=28%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六009 哈尔姆斯 vs 埃夫斯堡 [瑞超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="130" customHeight="1">
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：瑞超
+欧赔：0.00/0.00/0.00
+竞彩SP：3.85 / 3.25 / 1.78
+差值分析：P主=35% P平=27% P客=38%
+推荐：客胜 信心1/10 比分0-1(泊松) 半全场平负 大小球小2.5(41%) 备选半全场:负负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六010 盖斯 vs 代格福什 [瑞超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="130" customHeight="1">
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：瑞超
+欧赔：0.00/0.00/0.00
+竞彩SP：1.52 / 3.72 / 4.95
+差值分析：P主=48% P平=25% P客=27%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(44%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六011 勒沃库森 vs 汉堡 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="130" customHeight="1">
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：1.27/7.50/6.50
+竞彩SP：1.16 / 6.7 / 8.5
+差值分析：P主=55% P平=20% P客=25%
+推荐：主胜 信心4/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(74%) 备选半全场:负胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六012 拜仁 vs 科隆 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="130" customHeight="1">
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：10.50/1.15/8.50
+竞彩SP：10.5 / 1.15 / 8.5
+差值分析：P主=0% P平=0% P客=0%
+推荐：客胜 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
+让球:让0 —=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六013 海登海姆 vs 美因茨 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="130" customHeight="1">
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：1.82/3.70/4.45
+竞彩SP：1.65 / 4.15 / 3.55
+差值分析：P主=48% P平=23% P客=29%
+推荐：主胜 信心4/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(71%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六014 圣保利 vs 沃夫斯堡 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="130" customHeight="1">
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：2.68/2.52/3.55
+竞彩SP：2.53 / 3.52 / 2.22
+差值分析：P主=40% P平=25% P客=35%
+推荐：主胜 信心1/10 比分3-2(泊松) 半全场胜胜 大小球大2.5(73%) 备选半全场:负胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六015 柏林联合 vs 奥格斯堡 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="130" customHeight="1">
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：2.25/2.60/3.90
+竞彩SP：2.74 / 3.55 / 2.07
+差值分析：P主=39% P平=25% P客=36%
+推荐：主胜 信心1/10 比分2-1(泊松) 半全场胜胜 大小球大2.5(69%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六016 法兰克福 vs 斯图加特 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="130" customHeight="1">
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：3.35/1.90/4.25
+竞彩SP：3.32 / 4.3 / 1.68
+差值分析：P主=35% P平=25% P客=40%
+推荐：客胜 信心2/10 比分0-1(泊松) 半全场平负 大小球小2.5(47%) 备选半全场:负负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六017 不来梅 vs 多特蒙德 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="130" customHeight="1">
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：2.18/2.98/3.95
+竞彩SP：2.98 / 4.0 / 1.84
+差值分析：P主=35% P平=21% P客=43%
+推荐：客胜 信心2/10 比分1-3(泊松) 半全场负负 大小球大2.5(75%) 备选半全场:平负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六018 门兴 vs 霍芬海姆 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="130" customHeight="1">
+      <c r="B140" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：4.30/1.58/4.60
+竞彩SP：4.45 / 4.65 / 1.45
+差值分析：P主=34% P平=22% P客=44%
+推荐：客胜 信心2/10 比分2-3(泊松) 半全场负负 大小球大2.5(75%) 备选半全场:胜负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六019 弗赖堡 vs 莱红牛 [德甲] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="130" customHeight="1">
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：德甲
+欧赔：2.62/2.52/3.70
+竞彩SP：2.36 / 3.8 / 2.26
+差值分析：P主=38% P平=23% P客=39%
+推荐：客胜 信心2/10 比分1-2(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六020 切尔西 vs 曼城 [英足总杯] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="130" customHeight="1">
+      <c r="B156" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：英足总杯
+欧赔：0.00/0.00/0.00
+竞彩SP：4.5 / 3.82 / 1.55
+差值分析：P主=33% P平=22% P客=45%
+推荐：客胜 信心1/10 比分1-3(泊松) 半全场负负 大小球大2.5(69%) 备选半全场:平负
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六021 博德闪耀 vs 特罗姆瑟 [挪超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="130" customHeight="1">
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：挪超
+欧赔：0.00/0.00/0.00
+竞彩SP：1.29 / 4.9 / 6.7
+差值分析：P主=50% P平=24% P客=26%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(45%) 备选半全场:平胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="14" t="inlineStr">
+        <is>
+          <t>⚽ 周六022 赫尔火花 vs 雅罗 [芬超] —</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="130" customHeight="1">
+      <c r="B172" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时间：—
+联赛：芬超
+欧赔：0.00/0.00/0.00
+竞彩SP：2.15 / 2.95 / 3.08
+差值分析：P主=43% P平=27% P客=30%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场平胜 大小球小2.5(41%) 备选半全场:胜胜
+让球:让0 无让球=— </t>
+        </is>
+      </c>
+    </row>
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六023 AC奥卢 vs TPS图尔 [芬超] 00:00</t>
+          <t>⚽ 周六023 AC奥卢 vs TPS图尔 [芬超] —</t>
         </is>
       </c>
     </row>
     <row r="180" ht="130" customHeight="1">
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：00:00
+          <t xml:space="preserve">时间：—
 联赛：芬超
-欧赔(spf)：0.0 / 0.0 / 0.0
-差值分析：P主=0% P平=0% P客=0%
-推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
-让球:让0 —=— </t>
+欧赔：0.00/0.00/0.00
+竞彩SP：1.48 / 3.7 / 5.45
+差值分析：P主=48% P平=25% P客=26%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六024 布拉加 vs 阿马多拉 [葡超] 01:00</t>
+          <t>⚽ 周六024 布拉加 vs 阿马多拉 [葡超] —</t>
         </is>
       </c>
     </row>
     <row r="188" ht="130" customHeight="1">
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：01:00
+          <t xml:space="preserve">时间：—
 联赛：葡超
-欧赔(spf)：1.53 / 3.8 / 4.7
-差值分析：P主=52% P平=26% P客=22%
+欧赔：0.00/0.00/0.00
+竞彩SP：1.53 / 3.8 / 4.7
+差值分析：P主=54% P平=21% P客=25%
 推荐：主胜 信心4/10 比分3-1(泊松) 半全场胜胜 大小球大2.5(70%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六025 利雅胜利 vs 大阪钢巴 [亚冠乙] 01:45</t>
+          <t>⚽ 周六025 利雅胜利 vs 大阪钢巴 [亚冠乙] —</t>
         </is>
       </c>
     </row>
     <row r="196" ht="130" customHeight="1">
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：01:45
+          <t xml:space="preserve">时间：—
 联赛：亚冠乙
-欧赔(spf)：1.27 / 4.55 / 8.2
-差值分析：P主=50% P平=26% P客=24%
+欧赔：0.00/0.00/0.00
+竞彩SP：1.3 / 4.5 / 7.25
+差值分析：P主=50% P平=24% P客=26%
 推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(46%) 备选半全场:平胜
-让球:让-1 输盘=让胜 </t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六026 吉达国民 vs 拉斯永恒 [沙职] 02:00</t>
+          <t>⚽ 周六026 吉达国民 vs 拉斯永恒 [沙职] —</t>
         </is>
       </c>
     </row>
     <row r="204" ht="130" customHeight="1">
       <c r="B204" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：02:00
+          <t xml:space="preserve">时间：—
 联赛：沙职
-欧赔(spf)：0.0 / 0.0 / 0.0
-差值分析：P主=0% P平=0% P客=0%
-推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
-让球:让0 —=— </t>
+欧赔：0.00/0.00/0.00
+竞彩SP：1.15 / 6.1 / 10.5
+差值分析：P主=52% P平=23% P客=26%
+推荐：主胜 信心1/10 比分2-0(泊松) 半全场胜胜 大小球小2.5(48%) 备选半全场:平胜
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六027 里斯本 vs 吉维森特 [葡超] 03:30</t>
+          <t>⚽ 周六027 里斯本 vs 吉维森特 [葡超] —</t>
         </is>
       </c>
     </row>
     <row r="212" ht="130" customHeight="1">
       <c r="B212" s="15" t="inlineStr">
         <is>
-          <t>时间：03:30
+          <t xml:space="preserve">时间：—
 联赛：葡超
-欧赔(spf)：2.45 / 3.9 / 2.15
-差值分析：P主=38% P平=28% P客=34%
-推荐：主胜 信心2/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(42%) 备选半全场:平胜
-让球:让-2 输盘=让胜 让-2深盘·主胜可能不穿盘</t>
+欧赔：0.00/0.00/0.00
+竞彩SP：0.0 / 0.0 / 0.0
+差值分析：P主=0% P平=0% P客=0%
+推荐：客胜 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
+让球:让0 —=— </t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六028 埃斯托里 vs 本菲卡 [葡超] 03:30</t>
+          <t>⚽ 周六028 埃斯托里 vs 本菲卡 [葡超] —</t>
         </is>
       </c>
     </row>
     <row r="220" ht="130" customHeight="1">
       <c r="B220" s="15" t="inlineStr">
         <is>
-          <t>时间：03:30
+          <t xml:space="preserve">时间：—
 联赛：葡超
-欧赔(spf)：9.5 / 5.7 / 1.18
-差值分析：P主=25% P平=24% P客=52%
+欧赔：1.25/10.12/6.49
+竞彩SP：9.5 / 5.7 / 1.18
+差值分析：P主=30% P平=19% P客=52%
 推荐：客胜 信心4/10 比分1-4(泊松) 半全场负负 大小球大2.5(72%) 备选半全场:平负
-让球:让+2 输盘=让胜 让+2深盘·客胜可能不穿盘</t>
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六029 纽约红牛 vs 纽约城 [美职] 07:30</t>
+          <t>⚽ 周六029 纽约红牛 vs 纽约城 [美职] —</t>
         </is>
       </c>
     </row>
     <row r="228" ht="130" customHeight="1">
       <c r="B228" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：07:30
+          <t xml:space="preserve">时间：—
 联赛：美职
-欧赔(spf)：0.0 / 0.0 / 0.0
-差值分析：P主=0% P平=0% P客=0%
-推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
-让球:让0 —=— </t>
+欧赔：0.00/0.00/0.00
+竞彩SP：2.55 / 3.46 / 2.23
+差值分析：P主=39% P平=26% P客=35%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场平胜 大小球小2.5(43%) 备选半全场:平负
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="14" t="inlineStr">
         <is>
-          <t>⚽ 周六030 新英格兰 vs 明尼苏达 [美职] 07:30</t>
+          <t>⚽ 周六030 新英格兰 vs 明尼苏达 [美职] —</t>
         </is>
       </c>
     </row>
     <row r="236" ht="130" customHeight="1">
       <c r="B236" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">时间：07:30
+          <t xml:space="preserve">时间：—
 联赛：美职
-欧赔(spf)：0.0 / 0.0 / 0.0
-差值分析：P主=0% P平=0% P客=0%
-推荐：不投 信心1/10 比分—(泊松) 半全场— 大小球—(—) 备选半全场:—
-让球:让0 —=— </t>
+欧赔：0.00/0.00/0.00
+竞彩SP：2.16 / 3.2 / 2.83
+差值分析：P主=42% P平=27% P客=31%
+推荐：主胜 信心1/10 比分1-0(泊松) 半全场胜胜 大小球小2.5(43%) 备选半全场:平胜
+让球:让0 无让球=— </t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A107:B107"/>
     <mergeCell ref="A123:B123"/>
     <mergeCell ref="A1:B1"/>
@@ -7009,7 +6990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7086,34 +7067,36 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>周六011+周六012</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+          <t>周六011+周六013</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)</t>
+·海登海姆:主胜(1.65)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>2.92元</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="inlineStr">
-        <is>
-          <t>+46%</t>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>4元</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>1.91倍</t>
         </is>
       </c>
     </row>
@@ -7125,35 +7108,37 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>周六011+周六012+周六013</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+          <t>周六011+周六013+周六024</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)</t>
+·海登海姆:主胜(1.65)
+·布拉加:主胜(1.53)</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>6元</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>2.93倍</t>
         </is>
       </c>
     </row>
@@ -7165,121 +7150,38 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>周六011+周六012+周六013+周六016</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
+          <t>周六011+周六013+周六024+周六028</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)</t>
+·海登海姆:主胜(1.65)
+·布拉加:主胜(1.53)
+·埃斯托里:客胜(1.18)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>+228%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)
-·不来梅:客胜(1.78)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>12.02元</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>+501%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017+周六018</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>·勒沃库森:主胜(1.16)
-·拜仁:主胜(1.73)
-·海登海姆:主胜(1.78)
-·法兰克福:客胜(1.74)
-·不来梅:客胜(1.78)
-·门兴:客胜(1.50)</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>22.00元</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="inlineStr">
-        <is>
-          <t>+1000%</t>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>7元</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>3.46倍</t>
         </is>
       </c>
     </row>
@@ -7298,33 +7200,36 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012</t>
+          <t>周六011+周六013</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:3-2(6.0)
+·海登海姆:2-1(8.2)</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>74.40元</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>+3620%</t>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>100元</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>50.00倍</t>
         </is>
       </c>
     </row>
@@ -7336,33 +7241,37 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>比分</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013</t>
+          <t>周六011+周六013+周六024</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:3-2(6.0)
+·海登海姆:2-1(8.2)
+·布拉加:3-1(7.7)</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>379.00</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>491.00元</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>+24450%</t>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>758元</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>379.00倍</t>
         </is>
       </c>
     </row>
@@ -7388,33 +7297,37 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013</t>
+          <t>周六011+周六013+周六024</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:主胜(1.16)/—
+·海登海姆:主胜(1.65)/—
+·布拉加:主胜(1.53)/—</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>3.86元</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>+93%</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>6元</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>2.93倍</t>
         </is>
       </c>
     </row>
@@ -7426,49 +7339,47 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016</t>
+          <t>周六011+周六013+周六024+周六028</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:主胜(1.16)/—
+·海登海姆:主胜(1.65)/—
+·布拉加:主胜(1.53)/—
+·埃斯托里:客胜(1.18)/—</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>6.56元</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>+228%</t>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>7元</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>3.46倍</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>D. 半全场串关（从泊松比分推半全场）</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7478,33 +7389,35 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012</t>
+          <t>周六011+周六013</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:胜胜(2.2)\n·海登海姆:胜胜(2.2)</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="19" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>9.68元</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>+384%</t>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>10元</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>4.84倍</t>
         </is>
       </c>
     </row>
@@ -7516,33 +7429,35 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013</t>
+          <t>周六011+周六013+周六024</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:胜胜(2.2)\n·海登海姆:胜胜(2.2)\n·布拉加:胜胜(2.2)</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>10.65</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
-        <is>
-          <t>24.20元</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>+1110%</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>21元</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>10.65倍</t>
         </is>
       </c>
     </row>
@@ -7554,109 +7469,35 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016</t>
+          <t>周六011+周六013+周六024+周六028</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>·勒沃库森:胜胜(2.2)\n·海登海姆:胜胜(2.2)\n·布拉加:胜胜(2.2)\n·埃斯托里:负负(2.5)</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="19" t="n">
-        <v>30.25</v>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>26.62</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>2元</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>60.50元</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>+2925%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>5串1</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>133.10元</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>+6555%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>6串1</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>半全场</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>周六011+周六012+周六013+周六016+周六017+周六018</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>146.41</v>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>2元</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>292.82元</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>+14541%</t>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>53元</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>26.62倍</t>
         </is>
       </c>
     </row>
